--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,59 +927,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>98636</v>
+        <v>92815</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R4" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,54 +1048,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>92810</v>
+        <v>98643</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R5" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -927,59 +927,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>92823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R4" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,54 +1048,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>92823</v>
+        <v>98651</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R5" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92823</v>
+        <v>92828</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92828</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -927,54 +927,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R4" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1021,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,59 +1053,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>92831</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R5" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B2" t="n">
         <v>98659</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R2" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B3" t="n">
         <v>98659</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R3" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,59 +927,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R4" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,54 +1048,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>92831</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R5" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R2" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R3" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92838</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92838</v>
+        <v>92845</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92845</v>
+        <v>92847</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,54 +927,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B4" t="n">
-        <v>92847</v>
+        <v>98704</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R4" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1021,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,59 +1053,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>92833</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R5" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B2" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R2" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R3" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,59 +927,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>98704</v>
+        <v>92834</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R4" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +1006,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +1016,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,54 +1048,59 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>92833</v>
+        <v>98705</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R5" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R2" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R3" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92834</v>
+        <v>92837</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B2" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R2" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R3" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R2" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,10 +801,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R3" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92839</v>
+        <v>92843</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999699</v>
       </c>
       <c r="B2" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999781</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128997885</v>
       </c>
       <c r="B4" t="n">
-        <v>92843</v>
+        <v>92844</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>128999224</v>
       </c>
       <c r="B5" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999699</v>
+        <v>128999781</v>
       </c>
       <c r="B2" t="n">
         <v>98724</v>
@@ -705,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543309</v>
+        <v>543306</v>
       </c>
       <c r="R2" t="n">
-        <v>6715500</v>
+        <v>6715511</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +769,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,7 +801,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999781</v>
+        <v>128999699</v>
       </c>
       <c r="B3" t="n">
         <v>98724</v>
@@ -831,7 +831,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -850,10 +850,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543306</v>
+        <v>543309</v>
       </c>
       <c r="R3" t="n">
-        <v>6715511</v>
+        <v>6715500</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>15:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -927,54 +927,59 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128997885</v>
+        <v>128999224</v>
       </c>
       <c r="B4" t="n">
-        <v>92844</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543159</v>
+        <v>543276</v>
       </c>
       <c r="R4" t="n">
-        <v>6715424</v>
+        <v>6715478</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,7 +1011,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1016,12 +1021,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1048,59 +1053,54 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128999224</v>
+        <v>128997885</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>92844</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543276</v>
+        <v>543159</v>
       </c>
       <c r="R5" t="n">
-        <v>6715478</v>
+        <v>6715424</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128999781</v>
       </c>
       <c r="B2" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>128999699</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -930,7 +930,7 @@
         <v>128999224</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>98727</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1056,7 +1056,7 @@
         <v>128997885</v>
       </c>
       <c r="B5" t="n">
-        <v>92844</v>
+        <v>92847</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128999781</v>
+        <v>128995418</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>92369</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>543306</v>
+        <v>542972</v>
       </c>
       <c r="R2" t="n">
-        <v>6715511</v>
+        <v>6715725</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:33</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:33</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -801,59 +782,54 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128999699</v>
+        <v>128997885</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>93209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>4366</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>543309</v>
+        <v>543159</v>
       </c>
       <c r="R3" t="n">
-        <v>6715500</v>
+        <v>6715424</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -885,7 +861,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -895,12 +871,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:27</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -927,59 +903,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128999224</v>
+        <v>129001890</v>
       </c>
       <c r="B4" t="n">
-        <v>98727</v>
+        <v>92869</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4769</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>543276</v>
+        <v>542920</v>
       </c>
       <c r="R4" t="n">
-        <v>6715478</v>
+        <v>6715619</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1011,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1021,12 +992,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:03</t>
+          <t>16:23</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+          <t>Tre ex på upphällningen.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1053,54 +1024,61 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128997885</v>
+        <v>128998624</v>
       </c>
       <c r="B5" t="n">
-        <v>92847</v>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4366</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Karslund öster om v69, Falun, Karslund öster om v69, Falun, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>543159</v>
+        <v>543304</v>
       </c>
       <c r="R5" t="n">
-        <v>6715424</v>
+        <v>6715490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1142,12 +1120,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Inget påtagligt vitt mycel, hyfsat skarp smak och hallonsaftsliknande vätska. I kant på stigen. Både tall o gran i närheten.</t>
+          <t>Grovt skattat antal. På yta cirka 5x3 (1)m mellan och vid två stenblock. Cirka 11 m till närmaste snitsel för avverkning.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1156,6 +1134,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1171,6 +1150,1869 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128998917</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Falun, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>543293</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6715474</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Grovt uppskattat på ytterligare 3x3 m som fortsättning på det andra nyss rapporterade området.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128998965</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>543287</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6715491</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128999002</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>543287</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6715487</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På yta ungefär 1m2. Cirka 8 m till närmsta snitsel för avverkning.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128999224</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Karslund öster om v69, Karslund öster om v69, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>543276</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6715478</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Precis på yttergränsen för avverkningen, i linje med.</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128999283</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Falun, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>543298</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6715468</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>128999300</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Falun, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>543302</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6715473</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På cirka 1m2.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>128999389</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>543301</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6715496</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>128999513</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>543299</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6715494</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Grovt uppskattat antal. På yta cirka 3x3m.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128999600</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>543290</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6715491</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ett par meter från gräns för avverkning, snitsling.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128999699</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>543309</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6715500</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>15:27</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>På  någon m2, precis invid snitsel för avverkning.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>128999781</v>
+      </c>
+      <c r="B16" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>543306</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6715511</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Minst 15 plantor på mindre yta, ngr dm2.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>128999811</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>543292</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6715501</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På yta cirka 1x0,4 m.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>128999885</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>543293</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6715504</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:38</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>På någon m2.</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>128999986</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>543280</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6715517</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>På yta cirka 1x1 m.</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>129000200</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Klubbtäktsberget, Klubbtäktsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>543286</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6715522</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Falun</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Vika</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-09</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>På någon m2.</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Cecilia Rastad</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 36197-2025 artfynd.xlsx
+++ b/artfynd/A 36197-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128995418</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -900,6 +910,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128997885</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1021,6 +1036,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129001890</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1150,6 +1170,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998624</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1276,6 +1301,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998917</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1397,6 +1427,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128998965</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1526,6 +1561,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999002</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1652,6 +1692,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999224</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1773,6 +1818,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999283</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1898,6 +1948,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999300</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2019,6 +2074,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999389</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2145,6 +2205,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999513</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2257,6 +2322,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999600</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2383,6 +2453,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999699</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2509,6 +2584,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999781</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2635,6 +2715,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999811</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2761,6 +2846,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999885</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2887,6 +2977,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128999986</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3013,8 +3108,34 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>